--- a/artfynd/A 25147-2024 artfynd.xlsx
+++ b/artfynd/A 25147-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117835783</v>
+        <v>117835918</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>97754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577213</v>
+        <v>577341</v>
       </c>
       <c r="R2" t="n">
-        <v>6893944</v>
+        <v>6893871</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117835735</v>
+        <v>117835375</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>97754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -796,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577195</v>
+        <v>577023</v>
       </c>
       <c r="R3" t="n">
-        <v>6893956</v>
+        <v>6893946</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117835918</v>
+        <v>117835604</v>
       </c>
       <c r="B4" t="n">
-        <v>97754</v>
+        <v>104914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577341</v>
+        <v>577059</v>
       </c>
       <c r="R4" t="n">
-        <v>6893871</v>
+        <v>6893921</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117835375</v>
+        <v>117835735</v>
       </c>
       <c r="B5" t="n">
-        <v>97754</v>
+        <v>79590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,27 +1011,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577023</v>
+        <v>577195</v>
       </c>
       <c r="R5" t="n">
-        <v>6893946</v>
+        <v>6893956</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117835604</v>
+        <v>117835783</v>
       </c>
       <c r="B6" t="n">
-        <v>104914</v>
+        <v>79561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,31 +1112,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577059</v>
+        <v>577213</v>
       </c>
       <c r="R6" t="n">
-        <v>6893921</v>
+        <v>6893944</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117836028</v>
+        <v>117835970</v>
       </c>
       <c r="B7" t="n">
-        <v>97754</v>
+        <v>97740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577159</v>
+        <v>577352</v>
       </c>
       <c r="R7" t="n">
-        <v>6893840</v>
+        <v>6893913</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117835893</v>
+        <v>117835674</v>
       </c>
       <c r="B8" t="n">
-        <v>97740</v>
+        <v>79561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,31 +1323,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577341</v>
+        <v>577162</v>
       </c>
       <c r="R8" t="n">
-        <v>6893871</v>
+        <v>6893961</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117835970</v>
+        <v>117835855</v>
       </c>
       <c r="B9" t="n">
-        <v>97740</v>
+        <v>79590</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,27 +1432,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577352</v>
+        <v>577213</v>
       </c>
       <c r="R9" t="n">
-        <v>6893913</v>
+        <v>6893944</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117835855</v>
+        <v>117835893</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>97740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,26 +1537,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577213</v>
+        <v>577341</v>
       </c>
       <c r="R10" t="n">
-        <v>6893944</v>
+        <v>6893871</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117835674</v>
+        <v>117836028</v>
       </c>
       <c r="B11" t="n">
-        <v>79561</v>
+        <v>97754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,30 +1639,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>223591</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577162</v>
+        <v>577159</v>
       </c>
       <c r="R11" t="n">
-        <v>6893961</v>
+        <v>6893840</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 25147-2024 artfynd.xlsx
+++ b/artfynd/A 25147-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117835918</v>
+        <v>117835674</v>
       </c>
       <c r="B2" t="n">
-        <v>97754</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577341</v>
+        <v>577162</v>
       </c>
       <c r="R2" t="n">
-        <v>6893871</v>
+        <v>6893961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117835375</v>
+        <v>117835604</v>
       </c>
       <c r="B3" t="n">
-        <v>97754</v>
+        <v>104916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577023</v>
+        <v>577059</v>
       </c>
       <c r="R3" t="n">
-        <v>6893946</v>
+        <v>6893921</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117835604</v>
+        <v>117835375</v>
       </c>
       <c r="B4" t="n">
-        <v>104914</v>
+        <v>97756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577059</v>
+        <v>577023</v>
       </c>
       <c r="R4" t="n">
-        <v>6893921</v>
+        <v>6893946</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117835735</v>
+        <v>117836028</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>97756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,26 +1010,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577195</v>
+        <v>577159</v>
       </c>
       <c r="R5" t="n">
-        <v>6893956</v>
+        <v>6893840</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-06-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117835783</v>
+        <v>117835855</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117835970</v>
+        <v>117835918</v>
       </c>
       <c r="B7" t="n">
-        <v>97740</v>
+        <v>97756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220093</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577352</v>
+        <v>577341</v>
       </c>
       <c r="R7" t="n">
-        <v>6893913</v>
+        <v>6893871</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117835674</v>
+        <v>117835893</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>97742</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,30 +1323,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577162</v>
+        <v>577341</v>
       </c>
       <c r="R8" t="n">
-        <v>6893961</v>
+        <v>6893871</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1416,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117835855</v>
+        <v>117835735</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>79592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577213</v>
+        <v>577195</v>
       </c>
       <c r="R9" t="n">
-        <v>6893944</v>
+        <v>6893956</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1489,12 +1490,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2014-06-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117835893</v>
+        <v>117835970</v>
       </c>
       <c r="B10" t="n">
-        <v>97740</v>
+        <v>97742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577341</v>
+        <v>577352</v>
       </c>
       <c r="R10" t="n">
-        <v>6893871</v>
+        <v>6893913</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117836028</v>
+        <v>117835783</v>
       </c>
       <c r="B11" t="n">
-        <v>97754</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,31 +1640,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577159</v>
+        <v>577213</v>
       </c>
       <c r="R11" t="n">
-        <v>6893840</v>
+        <v>6893944</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 25147-2024 artfynd.xlsx
+++ b/artfynd/A 25147-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,6 +1731,118 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118920607</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96801</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sö. om Buskan, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577169</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6893796</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med frisk revlummer</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karin Svingstedt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karin Svingstedt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25147-2024 artfynd.xlsx
+++ b/artfynd/A 25147-2024 artfynd.xlsx
@@ -1736,7 +1736,7 @@
         <v>118920607</v>
       </c>
       <c r="B12" t="n">
-        <v>96801</v>
+        <v>96808</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
